--- a/notebooks/UO2_PKA_Radiation_Damage_Lab.xlsx
+++ b/notebooks/UO2_PKA_Radiation_Damage_Lab.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lanl-my.sharepoint.com/personal/372600_win_lanl_gov/Documents/SummerSchool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C34DC721-32AD-6D43-9E82-3B6D4600A16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{C34DC721-32AD-6D43-9E82-3B6D4600A16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0D98280-C594-D947-965D-DB85B8388B36}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="660" windowWidth="32380" windowHeight="20720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="1000" windowWidth="30240" windowHeight="20720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Run Log" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>PKA Radiation-Damage Dashboard</t>
   </si>
@@ -417,18 +417,6 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -436,6 +424,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,23 +506,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx2"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -553,8 +536,6 @@
           <c:dPt>
             <c:idx val="0"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -617,12 +598,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -685,12 +669,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -753,12 +740,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -821,12 +811,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -889,12 +882,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -957,12 +953,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1025,12 +1024,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1093,12 +1095,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1161,12 +1166,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1229,12 +1237,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1297,12 +1308,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1365,12 +1379,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1433,12 +1450,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1501,12 +1521,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1569,12 +1592,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1637,12 +1663,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="16"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1705,12 +1734,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="17"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1773,12 +1805,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="18"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1841,12 +1876,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="19"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1909,12 +1947,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000027-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="20"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -1977,12 +2018,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="21"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2045,12 +2089,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="22"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2113,12 +2160,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002D-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="23"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2181,12 +2231,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002F-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="24"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2249,12 +2302,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000031-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="25"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2317,12 +2373,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000033-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="26"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2385,12 +2444,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000035-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="27"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2453,12 +2515,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000037-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="28"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2521,12 +2586,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000039-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="29"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2589,12 +2657,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000003B-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="30"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2657,12 +2728,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000003D-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="31"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2725,12 +2799,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000003F-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="32"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2793,12 +2870,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000041-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="33"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2861,12 +2941,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000043-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="34"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2929,12 +3012,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000045-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="35"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -2997,12 +3083,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000047-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="36"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3065,12 +3154,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000049-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="37"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3133,12 +3225,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000004B-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="38"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3201,12 +3296,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000004D-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="39"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3269,12 +3367,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000004F-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="40"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3337,12 +3438,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000051-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="41"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3405,12 +3509,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000053-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="42"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3473,12 +3580,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000055-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="43"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3541,12 +3651,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000057-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="44"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3609,12 +3722,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000059-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="45"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3677,12 +3793,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000005B-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="46"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3745,12 +3864,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000005D-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="47"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3813,12 +3935,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000005F-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="48"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3881,12 +4006,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000061-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="49"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -3949,12 +4077,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000063-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="50"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4010,12 +4141,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000065-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="51"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4078,12 +4212,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000067-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="52"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4146,12 +4283,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000069-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="53"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4214,12 +4354,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000006B-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="54"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4282,12 +4425,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000006D-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="55"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4350,12 +4496,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000006F-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="56"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4418,12 +4567,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000071-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="57"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4486,12 +4638,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000073-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="58"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4554,12 +4709,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000075-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="59"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4622,12 +4780,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000077-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="60"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4690,12 +4851,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000079-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="61"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4758,12 +4922,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000007B-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="62"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4826,12 +4993,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000007D-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="63"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4894,12 +5064,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000007F-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="64"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -4962,12 +5135,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000081-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="65"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5030,12 +5206,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000083-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="66"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5098,12 +5277,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000085-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="67"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5166,12 +5348,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000087-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="68"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5234,12 +5419,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000089-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="69"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5302,12 +5490,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000008B-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="70"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5370,12 +5561,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000008D-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="71"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5438,12 +5632,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000008F-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="72"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5506,12 +5703,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000091-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="73"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5574,12 +5774,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000093-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="74"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5642,12 +5845,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000095-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="75"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5710,12 +5916,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000097-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="76"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5778,12 +5987,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000099-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="77"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5846,12 +6058,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000009B-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="78"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5914,12 +6129,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000009D-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="79"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -5982,12 +6200,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000009F-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="80"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6050,12 +6271,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A1-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="81"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6118,12 +6342,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A3-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="82"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6186,12 +6413,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A5-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="83"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6254,12 +6484,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A7-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="84"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6322,12 +6555,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A9-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="85"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6390,12 +6626,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000AB-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="86"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6458,12 +6697,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000AD-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="87"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6526,12 +6768,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000AF-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="88"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6594,12 +6839,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B1-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="89"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6662,12 +6910,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B3-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="90"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6730,12 +6981,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B5-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="91"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6798,12 +7052,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B7-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="92"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6866,12 +7123,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B9-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="93"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -6934,12 +7194,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000BB-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="94"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -7002,12 +7265,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000BD-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="95"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -7070,12 +7336,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000BF-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="96"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -7138,12 +7407,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000C1-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="97"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -7206,12 +7478,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000C3-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="98"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -7274,12 +7549,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000C5-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="99"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -7342,6 +7620,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000C7-63AC-9941-894A-EF0A7DB5A045}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:xVal>
             <c:numRef>
@@ -7350,22 +7633,22 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>58</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>60</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>100</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>150</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>#N/A</c:v>
@@ -7659,22 +7942,22 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>#N/A</c:v>
@@ -8031,23 +8314,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx2"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -8138,23 +8404,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx2"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -8283,23 +8532,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx2"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -8330,8 +8562,6 @@
           <c:dPt>
             <c:idx val="0"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -8394,12 +8624,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -8462,12 +8695,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -8530,12 +8766,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -8598,12 +8837,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -8666,12 +8908,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -8734,12 +8979,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -8802,12 +9050,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -8870,12 +9121,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -8938,12 +9192,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9006,12 +9263,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9074,12 +9334,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9142,12 +9405,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9210,12 +9476,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9278,12 +9547,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9346,12 +9618,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9414,12 +9689,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="16"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9482,12 +9760,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="17"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9550,12 +9831,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="18"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9618,12 +9902,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="19"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9686,12 +9973,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000027-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="20"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9754,12 +10044,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="21"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9822,12 +10115,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="22"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9890,12 +10186,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002D-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="23"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -9958,12 +10257,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002F-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="24"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10026,12 +10328,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000031-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="25"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10094,12 +10399,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000033-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="26"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10162,12 +10470,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000035-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="27"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10230,12 +10541,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000037-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="28"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10298,12 +10612,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000039-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="29"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10366,12 +10683,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000003B-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="30"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10434,12 +10754,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000003D-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="31"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10502,12 +10825,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000003F-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="32"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10570,12 +10896,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000041-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="33"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10638,12 +10967,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000043-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="34"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10706,12 +11038,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000045-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="35"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10774,12 +11109,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000047-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="36"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10842,12 +11180,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000049-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="37"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10910,12 +11251,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000004B-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="38"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -10978,12 +11322,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000004D-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="39"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11046,12 +11393,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000004F-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="40"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11114,12 +11464,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000051-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="41"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11182,12 +11535,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000053-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="42"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11250,12 +11606,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000055-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="43"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11318,12 +11677,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000057-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="44"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11386,12 +11748,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000059-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="45"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11454,12 +11819,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000005B-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="46"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11522,12 +11890,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000005D-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="47"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11590,12 +11961,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000005F-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="48"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11658,12 +12032,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000061-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="49"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11726,12 +12103,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000063-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="50"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11787,12 +12167,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000065-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="51"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11855,12 +12238,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000067-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="52"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11923,12 +12309,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000069-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="53"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -11991,12 +12380,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000006B-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="54"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12059,12 +12451,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000006D-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="55"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12127,12 +12522,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000006F-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="56"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12195,12 +12593,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000071-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="57"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12263,12 +12664,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000073-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="58"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12331,12 +12735,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000075-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="59"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12399,12 +12806,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000077-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="60"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12467,12 +12877,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000079-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="61"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12535,12 +12948,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000007B-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="62"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12603,12 +13019,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000007D-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="63"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12671,12 +13090,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000007F-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="64"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12739,12 +13161,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000081-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="65"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12807,12 +13232,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000083-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="66"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12875,12 +13303,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000085-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="67"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -12943,12 +13374,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000087-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="68"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13011,12 +13445,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000089-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="69"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13079,12 +13516,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000008B-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="70"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13147,12 +13587,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000008D-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="71"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13215,12 +13658,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000008F-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="72"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13283,12 +13729,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000091-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="73"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13351,12 +13800,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000093-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="74"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13419,12 +13871,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000095-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="75"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13487,12 +13942,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000097-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="76"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13555,12 +14013,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000099-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="77"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13623,12 +14084,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000009B-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="78"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13691,12 +14155,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000009D-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="79"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13759,12 +14226,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000009F-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="80"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13827,12 +14297,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A1-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="81"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13895,12 +14368,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A3-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="82"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -13963,12 +14439,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A5-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="83"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14031,12 +14510,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A7-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="84"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14099,12 +14581,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A9-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="85"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14167,12 +14652,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000AB-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="86"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14235,12 +14723,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000AD-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="87"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14303,12 +14794,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000AF-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="88"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14371,12 +14865,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B1-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="89"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14439,12 +14936,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B3-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="90"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14507,12 +15007,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B5-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="91"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14575,12 +15078,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B7-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="92"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14643,12 +15149,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B9-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="93"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14711,12 +15220,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000BB-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="94"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14779,12 +15291,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000BD-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="95"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14847,12 +15362,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000BF-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="96"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14915,12 +15433,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000C1-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="97"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -14983,12 +15504,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000C3-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="98"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -15051,12 +15575,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000C5-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="99"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -15119,6 +15646,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000C7-1514-8C4B-AD4F-61C7AC10F129}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:xVal>
             <c:numRef>
@@ -15127,22 +15659,22 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>58</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>60</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>100</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>150</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>#N/A</c:v>
@@ -15436,22 +15968,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>2.2099305786248399E-2</c:v>
+                  <c:v>0.1095</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.3328180212998002E-2</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.4877892547138999E-2</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.7540751118996004E-2</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.109510412074124</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.0578117760889698E-2</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>#N/A</c:v>
@@ -15808,23 +16340,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx2"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -15915,23 +16430,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx2"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.0000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -16060,23 +16558,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx2"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -16107,8 +16588,6 @@
           <c:dPt>
             <c:idx val="0"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16171,12 +16650,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16239,12 +16721,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16307,12 +16792,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16375,12 +16863,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16443,12 +16934,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16511,12 +17005,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16579,12 +17076,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16647,12 +17147,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16715,12 +17218,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16783,12 +17289,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16851,12 +17360,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16919,12 +17431,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -16987,12 +17502,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17055,12 +17573,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17123,12 +17644,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17191,12 +17715,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="16"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17259,12 +17786,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="17"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17327,12 +17857,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="18"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17395,12 +17928,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="19"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17463,12 +17999,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000027-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="20"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17531,12 +18070,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="21"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17599,12 +18141,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="22"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17667,12 +18212,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002D-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="23"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17735,12 +18283,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002F-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="24"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17803,12 +18354,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000031-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="25"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17871,12 +18425,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000033-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="26"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -17939,12 +18496,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000035-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="27"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18007,12 +18567,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000037-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="28"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18075,12 +18638,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000039-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="29"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18143,12 +18709,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000003B-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="30"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18211,12 +18780,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000003D-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="31"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18279,12 +18851,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000003F-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="32"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18347,12 +18922,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000041-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="33"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18415,12 +18993,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000043-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="34"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18483,12 +19064,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000045-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="35"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18551,12 +19135,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000047-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="36"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18619,12 +19206,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000049-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="37"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18687,12 +19277,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000004B-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="38"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18755,12 +19348,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000004D-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="39"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18823,12 +19419,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000004F-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="40"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18891,12 +19490,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000051-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="41"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -18959,12 +19561,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000053-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="42"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19027,12 +19632,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000055-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="43"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19095,12 +19703,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000057-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="44"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19163,12 +19774,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000059-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="45"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19231,12 +19845,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000005B-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="46"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19299,12 +19916,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000005D-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="47"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19367,12 +19987,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000005F-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="48"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19435,12 +20058,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000061-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="49"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19503,12 +20129,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000063-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="50"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19564,12 +20193,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000065-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="51"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19632,12 +20264,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000067-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="52"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19700,12 +20335,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000069-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="53"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19768,12 +20406,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000006B-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="54"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19836,12 +20477,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000006D-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="55"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19904,12 +20548,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000006F-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="56"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -19972,12 +20619,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000071-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="57"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20040,12 +20690,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000073-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="58"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20108,12 +20761,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000075-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="59"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20176,12 +20832,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000077-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="60"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20244,12 +20903,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000079-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="61"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20312,12 +20974,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000007B-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="62"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20380,12 +21045,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000007D-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="63"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20448,12 +21116,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000007F-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="64"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20516,12 +21187,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000081-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="65"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20584,12 +21258,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000083-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="66"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20652,12 +21329,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000085-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="67"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20720,12 +21400,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000087-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="68"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20788,12 +21471,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000089-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="69"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20856,12 +21542,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000008B-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="70"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20924,12 +21613,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000008D-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="71"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -20992,12 +21684,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000008F-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="72"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21060,12 +21755,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000091-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="73"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21128,12 +21826,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000093-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="74"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21196,12 +21897,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000095-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="75"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21264,12 +21968,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000097-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="76"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21332,12 +22039,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000099-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="77"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21400,12 +22110,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000009B-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="78"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21468,12 +22181,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000009D-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="79"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21536,12 +22252,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000009F-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="80"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21604,12 +22323,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A1-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="81"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21672,12 +22394,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A3-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="82"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21740,12 +22465,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A5-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="83"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21808,12 +22536,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A7-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="84"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21876,12 +22607,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000A9-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="85"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -21944,12 +22678,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000AB-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="86"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22012,12 +22749,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000AD-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="87"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22080,12 +22820,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000AF-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="88"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22148,12 +22891,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B1-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="89"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22216,12 +22962,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B3-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="90"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22284,12 +23033,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B5-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="91"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22352,12 +23104,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B7-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="92"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22420,12 +23175,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000B9-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="93"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22488,12 +23246,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000BB-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="94"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22556,12 +23317,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000BD-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="95"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22624,12 +23388,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000BF-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="96"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22692,12 +23459,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000C1-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="97"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22760,12 +23530,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000C3-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="98"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22828,12 +23601,15 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000C5-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="99"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
               <c:spPr>
                 <a:gradFill rotWithShape="1">
                   <a:gsLst>
@@ -22896,6 +23672,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{000000C7-CD5B-FC46-8257-D7C3001C8D6B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:xVal>
             <c:numRef>
@@ -22904,22 +23685,22 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>58</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>60</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>100</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>150</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>#N/A</c:v>
@@ -23213,22 +23994,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>0.36306022931034598</c:v>
+                  <c:v>4.7786999999999997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.38216227600000002</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.43541074400000002</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.8540936033099999</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.7787176921953698</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.1171577772211396</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>#N/A</c:v>
@@ -23585,23 +24366,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx2"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -23692,23 +24456,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx2"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.0000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -23790,1461 +24537,6 @@
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
-  <a:schemeClr val="accent3"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
-  <a:schemeClr val="accent3"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
-  <a:schemeClr val="accent3"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk2">
-        <a:lumMod val="75000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk2">
-        <a:lumMod val="75000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk2">
-        <a:lumMod val="75000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25646,36 +24938,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
     </row>
     <row r="2" spans="1:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -25709,7 +25001,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <f t="shared" ref="A5:A36" si="0">IF(D5="","",ROW()-4)</f>
+        <f>IF(D5="","",ROW()-4)</f>
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -25719,19 +25011,19 @@
         <v>110</v>
       </c>
       <c r="D5" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E5" s="5">
         <v>300</v>
       </c>
       <c r="F5" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" s="7">
-        <v>2.2099305786248399E-2</v>
+        <v>0.1095</v>
       </c>
       <c r="H5" s="7">
-        <v>0.36306022931034598</v>
+        <v>4.7786999999999997</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="7"/>
@@ -25739,152 +25031,70 @@
       <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="3">
-        <v>110</v>
-      </c>
-      <c r="D6" s="4">
-        <v>150</v>
-      </c>
-      <c r="E6" s="5">
-        <v>300</v>
-      </c>
-      <c r="F6" s="6">
-        <v>4</v>
-      </c>
-      <c r="G6" s="7">
-        <v>9.0578117760889698E-2</v>
-      </c>
-      <c r="H6" s="7">
-        <v>4.1171577772211396</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
       <c r="I6" s="6"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="8"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="3">
-        <v>110</v>
-      </c>
-      <c r="D7" s="4">
-        <v>100</v>
-      </c>
-      <c r="E7" s="5">
-        <v>300</v>
-      </c>
-      <c r="F7" s="6">
-        <v>5</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0.109510412074124</v>
-      </c>
-      <c r="H7" s="7">
-        <v>4.7787176921953698</v>
-      </c>
+      <c r="A7" s="2"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
       <c r="I7" s="6"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="8"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3">
-        <v>110</v>
-      </c>
-      <c r="D8" s="4">
-        <v>60</v>
-      </c>
-      <c r="E8" s="5">
-        <v>300</v>
-      </c>
-      <c r="F8" s="6">
-        <v>2</v>
-      </c>
-      <c r="G8" s="7">
-        <v>6.7540751118996004E-2</v>
-      </c>
-      <c r="H8" s="7">
-        <v>4.8540936033099999</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
       <c r="I8" s="6"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="8"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="3">
-        <v>110</v>
-      </c>
-      <c r="D9" s="4">
-        <v>55</v>
-      </c>
-      <c r="E9" s="5">
-        <v>300</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7">
-        <v>2.3328180212998002E-2</v>
-      </c>
-      <c r="H9" s="7">
-        <v>0.38216227600000002</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
       <c r="I9" s="6"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="8"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3">
-        <v>110</v>
-      </c>
-      <c r="D10" s="4">
-        <v>58</v>
-      </c>
-      <c r="E10" s="5">
-        <v>300</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7">
-        <v>2.4877892547138999E-2</v>
-      </c>
-      <c r="H10" s="7">
-        <v>0.43541074400000002</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
       <c r="I10" s="6"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -25892,7 +25102,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A6:A36" si="0">IF(D11="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B11" s="3"/>
@@ -27526,16 +26736,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
@@ -27555,9 +26765,9 @@
       <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="12" t="str">
         <f>IFERROR(_xlfn.AGGREGATE(14,6,'Run Log'!$D$5:$D$104/(('Run Log'!$B$5:$B$104=$B$4)*('Run Log'!$C$5:$C$104=$B$5)*('Run Log'!$F$5:$F$104=0)),1),"")</f>
-        <v>58</v>
+        <v/>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -27572,7 +26782,7 @@
       </c>
       <c r="E5" s="12">
         <f>IFERROR(_xlfn.AGGREGATE(15,6,'Run Log'!$D$5:$D$104/(('Run Log'!$B$5:$B$104=$B$4)*('Run Log'!$C$5:$C$104=$B$5)*('Run Log'!$F$5:$F$104&gt;0)),1),"")</f>
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -27581,7 +26791,7 @@
       </c>
       <c r="E6" s="12" t="str">
         <f>IF(OR(E4="",E5=""),"Add runs that bracket the transition",IF(E4&lt;E5,TEXT(E4,"0.0")&amp;" &lt; E_d &lt;= "&amp;TEXT(E5,"0.0")&amp;" eV","Run set does not cleanly bracket a threshold"))</f>
-        <v>58.0 &lt; E_d &lt;= 60.0 eV</v>
+        <v>Add runs that bracket the transition</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -27606,109 +26816,109 @@
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="15">
         <f>IF(AND('Run Log'!B5=$B$4,'Run Log'!C5=$B$5,'Run Log'!D5&lt;&gt;""),'Run Log'!D5,NA())</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="B10" s="15">
         <f>IF(AND('Run Log'!B5=$B$4,'Run Log'!C5=$B$5,'Run Log'!D5&lt;&gt;""),'Run Log'!F5,NA())</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" s="16">
         <f>IF(AND('Run Log'!B5=$B$4,'Run Log'!C5=$B$5,'Run Log'!D5&lt;&gt;""),'Run Log'!G5,NA())</f>
-        <v>2.2099305786248399E-2</v>
+        <v>0.1095</v>
       </c>
       <c r="D10" s="16">
         <f>IF(AND('Run Log'!B5=$B$4,'Run Log'!C5=$B$5,'Run Log'!D5&lt;&gt;""),'Run Log'!H5,NA())</f>
-        <v>0.36306022931034598</v>
+        <v>4.7786999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="15">
+      <c r="A11" s="15" t="e">
         <f>IF(AND('Run Log'!B9=$B$4,'Run Log'!C9=$B$5,'Run Log'!D9&lt;&gt;""),'Run Log'!D9,NA())</f>
-        <v>55</v>
-      </c>
-      <c r="B11" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="B11" s="15" t="e">
         <f>IF(AND('Run Log'!B9=$B$4,'Run Log'!C9=$B$5,'Run Log'!D9&lt;&gt;""),'Run Log'!F9,NA())</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="16">
+        <v>#N/A</v>
+      </c>
+      <c r="C11" s="16" t="e">
         <f>IF(AND('Run Log'!B9=$B$4,'Run Log'!C9=$B$5,'Run Log'!D9&lt;&gt;""),'Run Log'!G9,NA())</f>
-        <v>2.3328180212998002E-2</v>
-      </c>
-      <c r="D11" s="16">
+        <v>#N/A</v>
+      </c>
+      <c r="D11" s="16" t="e">
         <f>IF(AND('Run Log'!B9=$B$4,'Run Log'!C9=$B$5,'Run Log'!D9&lt;&gt;""),'Run Log'!H9,NA())</f>
-        <v>0.38216227600000002</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="15">
+      <c r="A12" s="15" t="e">
         <f>IF(AND('Run Log'!B10=$B$4,'Run Log'!C10=$B$5,'Run Log'!D10&lt;&gt;""),'Run Log'!D10,NA())</f>
-        <v>58</v>
-      </c>
-      <c r="B12" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="B12" s="15" t="e">
         <f>IF(AND('Run Log'!B10=$B$4,'Run Log'!C10=$B$5,'Run Log'!D10&lt;&gt;""),'Run Log'!F10,NA())</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="16">
+        <v>#N/A</v>
+      </c>
+      <c r="C12" s="16" t="e">
         <f>IF(AND('Run Log'!B10=$B$4,'Run Log'!C10=$B$5,'Run Log'!D10&lt;&gt;""),'Run Log'!G10,NA())</f>
-        <v>2.4877892547138999E-2</v>
-      </c>
-      <c r="D12" s="16">
+        <v>#N/A</v>
+      </c>
+      <c r="D12" s="16" t="e">
         <f>IF(AND('Run Log'!B10=$B$4,'Run Log'!C10=$B$5,'Run Log'!D10&lt;&gt;""),'Run Log'!H10,NA())</f>
-        <v>0.43541074400000002</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="15">
+      <c r="A13" s="15" t="e">
         <f>IF(AND('Run Log'!B8=$B$4,'Run Log'!C8=$B$5,'Run Log'!D8&lt;&gt;""),'Run Log'!D8,NA())</f>
-        <v>60</v>
-      </c>
-      <c r="B13" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="B13" s="15" t="e">
         <f>IF(AND('Run Log'!B8=$B$4,'Run Log'!C8=$B$5,'Run Log'!D8&lt;&gt;""),'Run Log'!F8,NA())</f>
-        <v>2</v>
-      </c>
-      <c r="C13" s="16">
+        <v>#N/A</v>
+      </c>
+      <c r="C13" s="16" t="e">
         <f>IF(AND('Run Log'!B8=$B$4,'Run Log'!C8=$B$5,'Run Log'!D8&lt;&gt;""),'Run Log'!G8,NA())</f>
-        <v>6.7540751118996004E-2</v>
-      </c>
-      <c r="D13" s="16">
+        <v>#N/A</v>
+      </c>
+      <c r="D13" s="16" t="e">
         <f>IF(AND('Run Log'!B8=$B$4,'Run Log'!C8=$B$5,'Run Log'!D8&lt;&gt;""),'Run Log'!H8,NA())</f>
-        <v>4.8540936033099999</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="15">
+      <c r="A14" s="15" t="e">
         <f>IF(AND('Run Log'!B7=$B$4,'Run Log'!C7=$B$5,'Run Log'!D7&lt;&gt;""),'Run Log'!D7,NA())</f>
-        <v>100</v>
-      </c>
-      <c r="B14" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="B14" s="15" t="e">
         <f>IF(AND('Run Log'!B7=$B$4,'Run Log'!C7=$B$5,'Run Log'!D7&lt;&gt;""),'Run Log'!F7,NA())</f>
-        <v>5</v>
-      </c>
-      <c r="C14" s="16">
+        <v>#N/A</v>
+      </c>
+      <c r="C14" s="16" t="e">
         <f>IF(AND('Run Log'!B7=$B$4,'Run Log'!C7=$B$5,'Run Log'!D7&lt;&gt;""),'Run Log'!G7,NA())</f>
-        <v>0.109510412074124</v>
-      </c>
-      <c r="D14" s="16">
+        <v>#N/A</v>
+      </c>
+      <c r="D14" s="16" t="e">
         <f>IF(AND('Run Log'!B7=$B$4,'Run Log'!C7=$B$5,'Run Log'!D7&lt;&gt;""),'Run Log'!H7,NA())</f>
-        <v>4.7787176921953698</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="15">
+      <c r="A15" s="15" t="e">
         <f>IF(AND('Run Log'!B6=$B$4,'Run Log'!C6=$B$5,'Run Log'!D6&lt;&gt;""),'Run Log'!D6,NA())</f>
-        <v>150</v>
-      </c>
-      <c r="B15" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="B15" s="15" t="e">
         <f>IF(AND('Run Log'!B6=$B$4,'Run Log'!C6=$B$5,'Run Log'!D6&lt;&gt;""),'Run Log'!F6,NA())</f>
-        <v>4</v>
-      </c>
-      <c r="C15" s="16">
+        <v>#N/A</v>
+      </c>
+      <c r="C15" s="16" t="e">
         <f>IF(AND('Run Log'!B6=$B$4,'Run Log'!C6=$B$5,'Run Log'!D6&lt;&gt;""),'Run Log'!G6,NA())</f>
-        <v>9.0578117760889698E-2</v>
-      </c>
-      <c r="D15" s="16">
+        <v>#N/A</v>
+      </c>
+      <c r="D15" s="16" t="e">
         <f>IF(AND('Run Log'!B6=$B$4,'Run Log'!C6=$B$5,'Run Log'!D6&lt;&gt;""),'Run Log'!H6,NA())</f>
-        <v>4.1171577772211396</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -27890,7 +27100,7 @@
         <f>IF(AND('Run Log'!B20=$B$4,'Run Log'!C20=$B$5,'Run Log'!D20&lt;&gt;""),'Run Log'!H20,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="E25" s="27"/>
+      <c r="E25" s="21"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="e">
@@ -29440,14 +28650,14 @@
       <c r="A1" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="19" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="17" t="s">
@@ -29455,10 +28665,10 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B4" s="26"/>
+      <c r="B4" s="20"/>
     </row>
     <row r="5" spans="1:6" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="19" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="17" t="s">
@@ -29466,10 +28676,10 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B6" s="26"/>
+      <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:6" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="19" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="17" t="s">
@@ -29477,10 +28687,10 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B8" s="26"/>
+      <c r="B8" s="20"/>
     </row>
     <row r="9" spans="1:6" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="19" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="17" t="s">
@@ -29488,10 +28698,10 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B10" s="26"/>
+      <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:6" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="19" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="17" t="s">
@@ -29499,10 +28709,10 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B12" s="26"/>
+      <c r="B12" s="20"/>
     </row>
     <row r="13" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="19" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="17" t="s">
@@ -29510,10 +28720,10 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B14" s="26"/>
+      <c r="B14" s="20"/>
     </row>
     <row r="15" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="17" t="s">
@@ -29521,10 +28731,10 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B16" s="26"/>
+      <c r="B16" s="20"/>
     </row>
     <row r="17" spans="2:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="19" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="18" t="s">

--- a/notebooks/UO2_PKA_Radiation_Damage_Lab.xlsx
+++ b/notebooks/UO2_PKA_Radiation_Damage_Lab.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lanl-my.sharepoint.com/personal/372600_win_lanl_gov/Documents/SummerSchool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{C34DC721-32AD-6D43-9E82-3B6D4600A16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0D98280-C594-D947-965D-DB85B8388B36}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{C34DC721-32AD-6D43-9E82-3B6D4600A16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13453998-EF09-2C46-A8E0-8F10FD93794B}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="1000" windowWidth="30240" windowHeight="20720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="700" windowWidth="30240" windowHeight="20720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Run Log" sheetId="1" r:id="rId1"/>
     <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
     <sheet name="Instructions" sheetId="3" r:id="rId3"/>
+    <sheet name="Tasks" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
@@ -424,8 +425,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -433,9 +432,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -24635,6 +24636,115 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>245807</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>20484</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>672927</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>102420</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F10FAEB-AE0E-F3AB-4987-227971CB0785}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1065162" y="4813710"/>
+          <a:ext cx="11898088" cy="4137742"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>245806</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>40967</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>566028</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>132062</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{002E5017-57B1-D212-520F-4748372DA308}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1065161" y="409677"/>
+          <a:ext cx="11791190" cy="4146901"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24938,36 +25048,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
     </row>
     <row r="4" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -25102,7 +25212,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="str">
-        <f t="shared" ref="A6:A36" si="0">IF(D11="","",ROW()-4)</f>
+        <f t="shared" ref="A11:A36" si="0">IF(D11="","",ROW()-4)</f>
         <v/>
       </c>
       <c r="B11" s="3"/>
@@ -26736,16 +26846,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
@@ -28647,14 +28757,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="19" t="s">
@@ -28748,4 +28858,14 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A88CEA-488B-094A-9D6A-4FC1AF5703EE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>